--- a/光伏配储项目/电价数据/2026/堤岸站.xlsx
+++ b/光伏配储项目/电价数据/2026/堤岸站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5071</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38422</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7411</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.56996</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5789</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.50026</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.491</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43715</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.4539</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43074</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.4219</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41476</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.4082</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39705</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39734</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38464</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40105</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42264</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41217</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35412</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39119</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38468</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41661</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.3918</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42033</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41358</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42356</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41198</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44267</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.34227</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.27181</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29541</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30588</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.29486</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.30894</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.09334000000000001</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.10132</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.08361</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.11126</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.0349</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.07748999999999999</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.08259999999999999</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.09098000000000001</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.06148</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08968999999999999</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.03608</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.01475</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14188</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21265</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.21974</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.21804</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.20973</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.03396</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.01773</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.21591</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.11808</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.24014</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.26336</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.27758</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.23801</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.17117</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.25237</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.51597</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.4063</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.48182</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.7166</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39207</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.61376</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.42639</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43524</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.41921</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.57278</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.45254</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.60488</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.78872</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.64671</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.59687</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.73358</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.85407</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.42027</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.66291</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.58817</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.64616</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.48407</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.44076</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.6233099999999999</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.5997400000000001</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.46937</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48059</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40276</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41625</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42597</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.68772</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.17704</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.67441</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.7565499999999999</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.7128300000000001</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5042</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5179</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50484</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50464</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48738</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40007</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46916</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37852</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37976</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39197</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33653</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37025</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35571</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37579</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37531</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38014</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41933</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.4987200000000001</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.5756100000000001</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.56376</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42969</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.34459</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38137</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34789</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.4111</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50763</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.15134</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29203</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35443</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.05951</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.29717</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30632</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29136</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.31495</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.4736</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.74021</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.9430499999999999</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.32054</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.36389</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.36675</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.36868</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.6699700000000001</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.44769</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.38623</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.14577</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.2875</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.28339</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.34906</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.47613</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.31796</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.30964</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.28476</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.22403</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.23479</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.41362</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.38876</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.29858</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.37834</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.33661</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.49341</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.59793</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.50734</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.66828</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.66144</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.7152000000000001</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.45132</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.43132</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.75313</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.4444</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.33226</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.58014</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.3444</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.42534</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.48707</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43396</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42746</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.39917</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37538</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35448</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.3347</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32141</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5082</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.40375</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.31421</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38151</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.39863</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36128</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39004</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38255</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36302</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42762</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44311</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37077</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39658</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36685</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36774</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35621</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36176</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35214</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36771</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35964</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38551</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39656</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44329</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43766</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34698</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39408</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35312</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36654</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34701</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.19973</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.2209</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.1989</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.31163</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.18675</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.16864</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.26533</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.31554</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31693</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.29715</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.47803</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.40155</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.5488099999999999</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.31694</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.48905</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.40767</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.30244</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.16587</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.30844</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.26855</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.30845</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.3001</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.28783</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.28922</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.37588</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.38517</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.39473</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.40227</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.45402</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.37787</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.42945</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.47932</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.36615</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.3844</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.33847</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.51206</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.5958</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.53462</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.6053099999999999</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.32595</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.44908</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.41589</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.46844</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.39687</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.43303</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.43212</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.45053</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.43749</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.38766</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.36764</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.41145</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.39254</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39563</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36083</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34867</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34206</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31891</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.40607</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.38392</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.29002</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.39998</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.39562</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.40661</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.37386</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.3654</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.40292</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.39887</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.37714</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.4481</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.37197</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.37842</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.37031</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.34413</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.34241</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.34154</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.34116</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.39688</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38918</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.3628</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.38734</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.4034700000000001</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.4307</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.44149</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.3541</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.25561</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34517</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.14854</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.23415</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.16257</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.34516</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.26177</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.16084</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30144</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.55957</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.2411</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.37283</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.28211</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.06541</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.05933</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.06226</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.36615</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.19048</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.20201</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.6418700000000001</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.06941</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.16907</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.28654</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.32086</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.4544</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.40769</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.42081</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.29061</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.28586</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.34232</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.16973</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.32712</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33602</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.33763</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33783</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.37679</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.36629</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.37792</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.40137</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.48843</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.4813</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.51981</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.42743</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.40687</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.40668</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.4287</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.3439700000000001</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.36372</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29307</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.29469</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.3122799999999999</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.29913</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29905</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.29194</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.32772</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38201</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30264</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31117</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.30639</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.31759</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31722</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31314</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30648</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31497</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29134</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29136</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29172</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29837</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.2931</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29605</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31245</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31303</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33257</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.28146</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26372</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.04529</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.06004</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.04441</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.04376</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04477</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.06244</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.05636</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.06054</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.02713</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04604</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.02711</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.03041</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.01998</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.02466</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.02869</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.028</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.01787</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.03532</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04051</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.02126</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.03526</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04004</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.03741</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04579</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.02231</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.02793</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21953</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.06422</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.07190000000000001</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05935</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.00419</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.14953</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.02871</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.0917</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29008</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29182</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29429</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33575</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33539</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38901</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39337</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38888</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.3776</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34158</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41074</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46819</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39707</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41869</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35823</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34471</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35513</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35167</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36811</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.6582899999999999</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40214</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42689</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42736</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.36061</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.36035</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.3579</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30967</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32726</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35754</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.36229</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.3465299999999999</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33563</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31809</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33171</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33773</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30085</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.3254</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33593</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.34064</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35166</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35263</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31702</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.1025</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04336</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04578</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.0462</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.0462</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.0462</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04547</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04397</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.01098</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.03604</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.11834</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.00551</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.01591</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.01526</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04154</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.0439</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04572</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04558</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04368</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04333</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04547</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04336</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.03474</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04533</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04523</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04537</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04356</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04421</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.0275</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.02959</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04998</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04989</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04793</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19972</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14271</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28991</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29463</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30452</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.2998</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.2949</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29278</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29324</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29221</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29675</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29073</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26874</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.2938</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30222</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34759</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34971</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34477</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36688</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36529</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33582</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31731</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40534</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35034</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32066</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30706</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29445</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17093</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15944</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15859</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23613</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26885</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27054</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30937</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35892</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29696</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37983</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42803</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45607</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.4183</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41513</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38902</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.4023</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30094</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29927</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29997</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15658</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29402</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31089</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31339</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31247</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34619</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30065</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.3854</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50766</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62203</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.7853300000000001</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49796</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78101</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92037</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49454</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91411</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86273</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29606</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35343</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88727</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63154</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18685</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.86871</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.54923</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33062</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03275</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5305700000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7908099999999999</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5332</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7727999999999999</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7774</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87675</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8737699999999999</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49299</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39851</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39967</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44975</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20677</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.8787999999999999</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.551</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62163</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53826</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49762</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45578</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42422</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.4371</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38811</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45267</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41977</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.3523</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40008</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36541</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38504</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41525</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43442</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34422</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39045</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34525</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40446</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34732</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45086</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35427</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40078</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40158</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5889500000000001</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42998</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59696</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60454</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6942</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46762</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.42042</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5831499999999999</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.88687</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.63813</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.84376</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.82329</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.8615499999999999</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44303</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.33646</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33287</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30574</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.29422</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.4313</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.30516</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.26673</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.3102200000000001</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35741</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33298</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33684</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30622</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31911</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34481</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31485</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.3156600000000001</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30409</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29643</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3122200000000001</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31403</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31224</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.31106</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32456</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35493</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34156</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33104</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33628</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41228</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41497</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45538</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41737</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39336</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37679</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35407</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9206799999999999</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36157</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46781</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.37088</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.41353</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.47147</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38274</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.41188</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36311</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.36852</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.35149</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34861</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.39015</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50392</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35821</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38956</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34446</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35647</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.3722</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35922</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36436</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31739</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31415</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.35062</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31524</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31191</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29082</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30715</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28779</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.29625</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16299</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.3031</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30856</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.33105</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.3055</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.32036</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29794</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26195</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19901</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27741</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19466</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31197</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.2782</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31161</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31204</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35223</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31531</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.32092</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30733</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31735</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29533</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31241</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29178</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30907</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31459</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29011</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34928</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25573</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.34647</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33832</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27658</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32977</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31077</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.34085</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38718</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.35387</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4483</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35111</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.41001</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42338</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.4512</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.34251</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42236</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35966</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40379</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40262</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.6030599999999999</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35286</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.89215</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.35781</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.16603</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7017100000000001</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79277</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6688200000000001</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58893</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45606</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45185</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50231</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.44137</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.44011</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.4164</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41418</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42592</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.50529</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41417</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43547</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41577</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43559</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39144</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.43148</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45442</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39746</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42476</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43766</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41417</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41403</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40299</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42705</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.40039</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40559</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49687</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36389</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29718</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36875</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.36914</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.31075</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30729</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30443</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.54325</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.36306</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.31367</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24962</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.35889</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.11609</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27325</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27005</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.3008</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26213</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25552</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30643</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28225</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28462</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.29063</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29199</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.31068</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31285</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32361</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.33191</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31611</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34152</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.40454</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40235</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36117</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33721</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.36857</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.34707</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36414</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.36683</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36309</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34983</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.4658</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.86838</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46824</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43945</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37664</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42869</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38711</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.3698</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.3343</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34167</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32532</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42578</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34546</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34254</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33539</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32799</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.33122</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32664</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32666</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31559</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32298</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31012</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31104</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32593</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32263</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.3951</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35239</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.40356</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37834</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35101</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33859</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35675</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.28608</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33408</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.30665</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.27522</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.28983</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.27648</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.22027</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.13636</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14238</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28012</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15103</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14137</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.13475</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14116</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.13388</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.2418</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.13381</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25124</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.25359</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.13078</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.08946999999999999</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.10494</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.10539</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.11554</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.1323</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.13635</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.27185</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.35496</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.3467</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34414</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38117</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34769</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40004</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36174</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38638</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45265</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40162</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39259</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40339</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39892</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45687</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44245</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.44163</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44662</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.4446</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40278</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39077</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39791</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39173</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.3611</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34998</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.54348</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38929</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.47189</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42591</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41789</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.3717200000000001</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38235</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38103</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39443</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38015</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38196</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36134</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.3931</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37178</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38221</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35139</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34835</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35637</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34587</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34113</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34113</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34589</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35848</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37199</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38223</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34106</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34149</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34126</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32874</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34309</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.36239</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.2978</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31483</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31393</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28235</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.27256</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26563</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.1916</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30925</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.24614</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24164</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26981</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30089</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.2883</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31788</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31411</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.34292</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.28963</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28411</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24241</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.3152</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30808</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.3239</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30533</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28587</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33526</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32742</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32667</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.31571</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34249</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35226</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.35437</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36689</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.41603</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.39427</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.37506</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.26135</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.34776</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38132</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41686</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.32377</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.35063</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36789</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37058</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36073</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38223</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38212</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38687</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36135</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36698</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.42242</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37108</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39607</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38162</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35337</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34257</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34865</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34709</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35057</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34166</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34278</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34343</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33888</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34142</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33455</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35099</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34661</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36244</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31978</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32868</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32691</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.28161</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.39872</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.30558</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.40173</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.44084</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.42855</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.32317</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.29683</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.3737799999999999</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.04284</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25262</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.24381</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.07501000000000001</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.22217</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.26916</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.27711</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.30822</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.30906</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.27901</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.29553</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.30769</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.30518</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.29221</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.34027</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.35248</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.33932</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.3239</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.4127</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.33239</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.33485</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35285</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31517</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.38651</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32497</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.31767</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.32796</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.43535</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.41577</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.6904400000000001</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36172</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.37695</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33738</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.32666</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.31966</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.5076499999999999</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.22269</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.38071</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30149</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31229</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32673</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.30406</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.31525</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.30962</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.29248</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30504</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.33254</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.3269</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33294</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32916</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32982</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.31962</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32467</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32547</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32793</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32878</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32456</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.3338</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32955</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32238</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.32048</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32365</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32772</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33857</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.34156</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32342</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33498</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34471</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34922</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33538</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.31761</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32417</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32302</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32489</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31935</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34226</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.30593</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34845</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34586</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31739</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28397</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32685</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32399</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32771</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33518</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33351</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32121</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.3218</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31315</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35162</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.3046</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.28906</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.32071</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36336</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34202</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33511</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.3638</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.33277</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.39773</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.38923</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.38117</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.38877</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.38235</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.39418</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.42379</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38778</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37231</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.41781</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35566</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38192</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.38549</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36425</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.3542</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.35167</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.35027</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.3511</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.3519</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35147</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.3468</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36763</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34759</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35617</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.35074</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33838</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37098</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33943</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.3409700000000001</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34567</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.35065</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.3414</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32943</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30947</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32693</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.33111</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32153</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33308</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32604</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37404</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32343</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.30436</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32564</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32791</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32148</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32458</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.33053</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33237</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33321</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34539</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35967</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.3416</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.3563</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36697</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35049</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.3605</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34638</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35941</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36145</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34935</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38335</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.38045</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38212</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38582</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.44063</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41202</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38068</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37642</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65696</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.78264</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.45509</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.28568</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.46098</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35093</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34542</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32122</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41169</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37689</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37192</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36264</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36125</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35346</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36061</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36133</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35671</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35269</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37257</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35939</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35713</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.38039</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.3665</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38048</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35709</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35251</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35847</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33026</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33535</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26623</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14856</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30402</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28309</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19714</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.26014</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27728</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.30543</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27919</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.21381</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.25291</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28392</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27582</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28908</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.28926</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30448</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.31177</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32249</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.16028</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29171</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.28819</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34444</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32328</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33637</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.33496</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.35209</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.33399</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.36367</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.36414</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31774</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.36631</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.4414</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.39481</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.44147</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.66575</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.62164</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.6349199999999999</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.51913</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.8546900000000001</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.49756</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.8547100000000001</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.48755</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.50338</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.4152</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.39393</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.3742</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.48981</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43301</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.42125</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37545</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36835</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.3611</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34508</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49269</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.5315</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.48341</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.48938</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41876</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39931</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40442</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41197</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40984</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41839</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40041</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39517</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.4123</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.41005</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39577</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38887</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.42182</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38975</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41932</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39221</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40256</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.4022</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41553</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40227</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45542</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45344</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.5688500000000001</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.50687</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45518</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.49075</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.45248</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.44482</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38511</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.39849</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.43595</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.42576</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.5180800000000001</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.4357</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.29928</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.3687</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.40458</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.40053</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.40943</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.3256</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.33817</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.29577</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.31501</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.32342</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.34921</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.36833</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.6153</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.37027</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.34213</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.18635</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.2849</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.33615</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.34283</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.30713</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33658</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37768</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.37359</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35624</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.35946</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35375</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.38463</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33821</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.41408</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.43834</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.49613</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.4414</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.52818</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.52552</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.57151</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.72212</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.74493</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.02812</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.8315399999999999</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.8169</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.5886</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.5282</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.8428300000000001</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7694299999999999</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6234700000000001</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.67198</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.4407</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47336</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.48571</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.48028</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.47278</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41925</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5562699999999999</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42997</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44433</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45857</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43466</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42474</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44825</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41638</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40084</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45887</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39983</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40696</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39888</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38762</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37921</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37441</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36067</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35747</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36644</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.38428</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37314</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36171</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36644</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38848</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39241</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36181</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.38006</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.37313</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38957</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.40117</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39802</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.3877</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35246</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.37183</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34738</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.34223</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.37984</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.18239</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.3847</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.35302</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35228</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40804</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.36531</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.46283</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.40244</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.4718</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.33254</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.10603</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18175</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30647</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.30043</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35712</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35222</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.37525</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.38196</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37655</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38339</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41966</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.37429</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.4333</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.4164</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41725</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38399</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.37832</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38987</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39533</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.41329</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.41273</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.37477</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37673</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39921</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36067</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.38102</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.40207</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.3845</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37671</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36397</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.40016</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.3851</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36925</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.4489</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39664</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39642</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35559</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.38257</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.38667</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35868</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.36646</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.36298</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35404</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34923</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35193</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.3532</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33491</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34323</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34906</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33756</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33411</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33645</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33701</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31356</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30569</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.27056</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.23104</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28761</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.22788</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.28701</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.24758</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.24414</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.14527</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29302</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29816</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.30921</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.24728</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04421</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25041</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.27772</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.16587</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18407</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.27404</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31352</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.29986</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.23204</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.25776</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26273</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.2361</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27736</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28513</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28784</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.33308</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.33054</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35583</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35331</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36292</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35513</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.36346</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.37633</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.3645</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34519</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.36223</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35989</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.38142</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35672</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.37317</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37321</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34686</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36662</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.38008</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34222</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36554</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37242</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36443</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35173</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34921</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35243</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32389</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33843</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34207</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34399</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33932</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32592</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.32104</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31835</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31484</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31497</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31768</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.3177</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.31359</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.31359</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.31603</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.31359</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.31398</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31318</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.33909</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.2265</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.28855</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.27059</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01843</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00033</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00614</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04968</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.15521</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02962</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03968</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04969</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01555</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04411</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04231</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04886</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04856</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02442</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.03055</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04971</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.01861</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04969</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.0497</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.0495</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00178</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.29451</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04974</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04934</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.0497</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03063</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01408</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04969</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04979</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03454</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.213</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.2805299999999999</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.30082</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.2796</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.32289</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.32497</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.32931</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.35134</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.3616</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.35574</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.36425</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.32362</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.37643</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.37091</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.37249</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.36474</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.36865</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.36522</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.39997</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.48416</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.40192</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.3752799999999999</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.37887</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.36935</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.36988</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.39672</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.41641</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.39651</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.9808300000000001</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.94926</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.46718</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.59358</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.4685</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.48201</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.55591</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.40219</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.41223</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.37616</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.42676</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.38863</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.39774</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.41691</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.36989</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.38947</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.43397</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.41847</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.37536</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.41739</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.38146</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.39937</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.42145</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.44169</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.46463</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.42785</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.37821</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.37159</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.38113</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.46062</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.99702</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.06434</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.93288</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.9704299999999999</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.36066</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.4258</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.20467</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.36264</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.36546</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.34853</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28611</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.37698</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.21262</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.25372</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.32289</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.01233</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00614</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.35582</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.35778</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.0814</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.33862</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.36346</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25374</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29161</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.2745</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.31284</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32674</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32459</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33606</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33229</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33479</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32919</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35439</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.37682</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.34028</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.38784</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.38953</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.39557</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.38073</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.37563</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.36908</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35145</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36876</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.38146</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32892</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32458</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35936</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.3639</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.26166</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.32592</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33691</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33464</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.33301</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.35677</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.4051</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.35521</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.33709</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.34145</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.37818</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.36788</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.36114</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.49433</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.52208</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.39339</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.40749</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32537</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.34803</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.31962</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.4804</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.38703</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.37464</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.39514</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.3641</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.44062</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.37694</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.36512</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.35648</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.43404</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.32256</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30555</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32072</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.3258</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31046</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14025</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27408</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.26991</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32685</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.34573</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.32736</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.29904</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29102</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31214</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32745</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32541</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.3455299999999999</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34649</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35492</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.35086</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33521</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33518</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.36673</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.36321</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.39916</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.36115</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.36346</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.35598</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35142</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36374</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35294</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31175</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33191</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33055</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33471</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33441</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.34709</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31941</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32281</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.33162</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33276</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33708</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34592</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.37635</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34068</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32671</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32517</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.34116</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34755</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34148</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36986</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35682</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.37068</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.35543</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33253</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35369</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.46343</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.31941</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.46807</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.41589</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.4939</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.37191</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36325</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35204</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.35206</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.30436</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.3434700000000001</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.39004</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30731</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.32963</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.25489</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.32873</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34695</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32187</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.2768</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32997</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33168</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.38762</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.38375</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47278</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.47694</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.37558</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.36724</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.40923</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.4412</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.40153</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.38923</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.46832</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.35742</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.5714600000000001</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.37943</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.35467</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.38458</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.3996499999999999</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.37437</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41578</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.46027</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40214</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.3732200000000001</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.40269</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.24863</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3735</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36932</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.47907</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40244</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39297</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38183</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36117</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37664</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.3747</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37983</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37821</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.37024</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36736</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.36119</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3611</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.3562</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34934</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37142</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.40113</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37618</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36679</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.3586</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35475</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.35479</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.38679</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.38744</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.36411</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.42994</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37586</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.36976</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.35307</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35564</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.3096</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36337</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.25871</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.37547</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.35677</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29294</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.30685</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.32398</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33412</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.30621</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31739</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.3444</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.30809</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33239</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33552</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34352</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.38149</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.37404</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.38025</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36075</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.38561</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.42171</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.38472</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.40028</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.42598</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.42488</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.49205</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.57024</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.55583</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.42788</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.56179</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.6210800000000001</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.49512</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.51964</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.5598099999999999</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.46762</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.60626</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.7290399999999999</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.69678</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.61211</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.53059</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.53716</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39834</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44144</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39672</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.3742799999999999</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.3778</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36805</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37354</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.29885</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.37051</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.37629</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36683</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.36523</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.35258</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.3481</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.36825</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.35663</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.35059</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35628</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.40775</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.35712</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.34328</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.36469</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.36421</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.36318</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.35368</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.35584</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.35733</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.34929</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.36739</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.38266</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.36931</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.38822</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.39716</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.37571</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.37095</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.36913</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.36547</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.3538</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.37593</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.37715</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.35523</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.33756</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.13492</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.24506</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.27455</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.05512</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.29118</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.31197</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.12196</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.02379</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.19862</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.15569</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.01525</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.28425</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.25673</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.14463</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.05781</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.03298</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.05982</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.17787</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.06667000000000001</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.05374</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.21322</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.15323</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.18659</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.35635</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.35615</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.32417</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.34826</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.36213</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.34642</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.34295</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.37854</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36396</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.36998</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.3899</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.43607</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.40741</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.48032</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.44767</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.3767799999999999</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39033</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.41506</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.38912</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.3825</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.42145</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37456</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.43052</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38419</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37715</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.36225</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.36146</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.38778</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.06047</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.39497</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.5617300000000001</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.51407</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.41691</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.3906</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.45761</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.41482</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.41372</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.39963</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.3998</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.39579</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.38757</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.38808</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.39182</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.39917</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.39688</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.38675</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.3858</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.38581</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.38458</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.3881</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.37753</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.37288</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.3917</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.3769</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.39611</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.38187</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.36474</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.37698</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.37869</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.38937</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.38637</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.37791</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.35636</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.3781600000000001</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36549</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.36319</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.14583</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.02353</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.02239</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.02091</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.01785</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.26971</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.04679999999999999</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00224</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01515</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.05096</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.00729</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>-0.00344</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.02033</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.15415</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.30166</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.04787</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.34135</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.18994</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.36737</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32224</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.32539</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.3619</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.36543</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34411</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.36112</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.40289</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.39983</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.44275</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.41459</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.40751</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36298</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37331</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39101</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36555</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.36705</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.42773</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.38521</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38621</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.40034</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.37873</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.40193</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.36326</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.38044</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.34673</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.37803</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.4054</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.37653</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38334</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.35442</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.37051</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.37107</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.35121</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.49058</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.39892</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.40064</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.39066</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.38601</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.39054</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.4045</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.38849</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.38886</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.38348</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.38096</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.38176</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.38003</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.36132</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.38287</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.37805</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.37945</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.37765</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.37307</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.37031</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.37281</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.37493</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.36947</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3534</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.3772799999999999</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.37098</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.37055</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.30193</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.18312</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.28463</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.30767</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.15251</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.20855</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.12052</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.22129</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04746</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.05232</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.05143</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.05062</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.05067</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.04722999999999999</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.10336</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03582</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.0825</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.13773</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.23864</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.27902</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.16185</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.37885</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.32467</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.16694</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.06057999999999999</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.31868</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.20928</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.15135</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.2937</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.2586</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.34428</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.34224</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.27777</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.37033</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.37144</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.39938</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.36927</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.37376</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.37798</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.40012</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.3566</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.36652</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.36382</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.38723</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.38793</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.3882</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.38671</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.40958</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.39531</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.38698</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.40883</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.48111</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39699</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.39498</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.39309</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.3972</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.37702</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.38897</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.39434</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.39744</v>
       </c>
     </row>
   </sheetData>
